--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5507,6 +5507,230 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125683113</v>
+      </c>
+      <c r="B45" t="n">
+        <v>74888</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229651</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglavsknapp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Plectocarpon lichenum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Sommerf.) D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storlidmyran, Storlidmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>658530</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7177097</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125683098</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storlidmyran, Storlidmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>658530</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7177097</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -5512,12 +5512,7 @@
         <v>125683113</v>
       </c>
       <c r="B45" t="n">
-        <v>74888</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>74929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,12 +5619,7 @@
         <v>125683098</v>
       </c>
       <c r="B46" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>125683113</v>
       </c>
       <c r="B45" t="n">
-        <v>74929</v>
+        <v>74930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>125683098</v>
       </c>
       <c r="B46" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -5619,7 +5619,7 @@
         <v>125683098</v>
       </c>
       <c r="B46" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>125683113</v>
       </c>
       <c r="B45" t="n">
-        <v>74930</v>
+        <v>74931</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>125683098</v>
       </c>
       <c r="B46" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 28719-2021 artfynd.xlsx
+++ b/artfynd/A 28719-2021 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>125683113</v>
       </c>
       <c r="B45" t="n">
-        <v>74931</v>
+        <v>74935</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>125683098</v>
       </c>
       <c r="B46" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
